--- a/SGC-CKN/Excel/a72108e8-eb17-4002-8602-cec9be8c5533_Thi_công_cọc_khoan_nhồi_đại_trà_lô_đất_ký_hiệu_CT-02_P11-02_D800_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/a72108e8-eb17-4002-8602-cec9be8c5533_Thi_công_cọc_khoan_nhồi_đại_trà_lô_đất_ký_hiệu_CT-02_P11-02_D800_21-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
@@ -165,21 +165,17 @@
     <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">22:25
-21/03/2026</t>
-  </si>
-  <si>
-    <t>Chạm sỏi</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">22:26
 21/03/2026</t>
+  </si>
+  <si>
+    <t>Chạm sỏi</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">23:45
@@ -1371,13 +1367,13 @@
         <v>-45.8</v>
       </c>
       <c r="H17" s="25">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I17" s="25">
         <v>7.2</v>
       </c>
       <c r="J17" s="12">
-        <v>7.85</v>
+        <v>7.71</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>49</v>
@@ -1394,10 +1390,10 @@
         <v>51</v>
       </c>
       <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>52</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>53</v>
       </c>
       <c r="F18" s="28">
         <v>-45.8</v>
@@ -1415,12 +1411,12 @@
         <v>3.36</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1526,31 +1522,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1747,13 +1743,13 @@
         <v>-45.8</v>
       </c>
       <c r="G8" s="25">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H8" s="25">
         <v>7.2</v>
       </c>
       <c r="I8" s="12">
-        <v>7.85</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1787,7 +1783,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
@@ -1805,13 +1801,13 @@
         <v>-50.23</v>
       </c>
       <c r="G10" s="33">
-        <v>5.23</v>
+        <v>5.25</v>
       </c>
       <c r="H10" s="33">
         <v>48.63</v>
       </c>
       <c r="I10" s="33">
-        <v>9.29</v>
+        <v>9.26</v>
       </c>
     </row>
   </sheetData>
